--- a/etf_holdings/2026-10-08_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-08_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:03</t>
+          <t>2026-10-08 23:44:57</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0%2585</t>
+          <t>-1.35%2550</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-1.35%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2585</v>
+        <v>2550</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>13.70%4,200,000</t>
+          <t>13.73%4,200,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>13.70%</t>
+          <t>13.73%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:03</t>
+          <t>2026-10-08 23:44:57</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-0.75%5950</t>
+          <t>+0.84%6000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-0.75%</t>
+          <t>+0.84%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5950</v>
+        <v>6000</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10.13%1,350,000</t>
+          <t>10.38%1,350,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>10.13%</t>
+          <t>10.38%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:03</t>
+          <t>2026-10-08 23:44:57</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.38%1305</t>
+          <t>-2.68%1270</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.38%</t>
+          <t>-2.68%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1305</v>
+        <v>1270</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8.69%5,280,000</t>
+          <t>8.60%5,280,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>8.69%</t>
+          <t>8.60%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:03</t>
+          <t>2026-10-08 23:44:57</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-2.1%514</t>
+          <t>+3.5%532</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-2.1%</t>
+          <t>+3.5%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>514</v>
+        <v>532</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7.59%11,700,000</t>
+          <t>7.98%11,700,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>7.59%</t>
+          <t>7.98%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>+0.27%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:03</t>
+          <t>2026-10-08 23:44:57</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -748,38 +748,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2059川湖</t>
+          <t>8046南電</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-10%11790</t>
+          <t>-0.34%1475</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-0.34%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>11790</v>
+        <v>1475</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6.99%470,000</t>
+          <t>6.43%3,400,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6.99%</t>
+          <t>6.43%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>470000</v>
+        <v>3400000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.77%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:03</t>
+          <t>2026-10-08 23:44:57</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -809,38 +809,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2454聯發科</t>
+          <t>2059川湖</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-1.73%4835</t>
+          <t>-9.97%10615</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>-9.97%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>4835</v>
+        <v>10615</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6.71%1,100,000</t>
+          <t>6.40%470,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>6.71%</t>
+          <t>6.40%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1100000</v>
+        <v>470000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>-0.70%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:03</t>
+          <t>2026-10-08 23:44:57</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,25 +875,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+2.8%1100</t>
+          <t>-2.27%1075</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+2.8%</t>
+          <t>-2.27%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1100</v>
+        <v>1075</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>6.41%4,620,000</t>
+          <t>6.37%4,620,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>6.41%</t>
+          <t>6.37%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:03</t>
+          <t>2026-10-08 23:44:57</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>2454聯發科</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-1.66%1480</t>
+          <t>-3%4690</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-1.66%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1480</v>
+        <v>4690</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>6.35%3,400,000</t>
+          <t>6.31%1,050,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>6.35%</t>
+          <t>6.31%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>3400000</v>
+        <v>1050000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:03</t>
+          <t>2026-10-08 23:44:57</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-3.8%3545</t>
+          <t>-2.96%3440</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-2.96%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>3545</v>
+        <v>3440</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5.59%1,250,000</t>
+          <t>5.51%1,250,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>5.59%</t>
+          <t>5.51%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:03</t>
+          <t>2026-10-08 23:44:57</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,25 +1058,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+3.52%647</t>
+          <t>-1.85%635</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+3.52%</t>
+          <t>-1.85%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>647</v>
+        <v>635</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.73%5,800,000</t>
+          <t>4.72%5,800,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.73%</t>
+          <t>4.72%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:03</t>
+          <t>2026-10-08 23:44:57</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+7.17%314</t>
+          <t>-1.27%310</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+7.17%</t>
+          <t>-1.27%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.37%8,500,000</t>
+          <t>3.38%8,500,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.37%</t>
+          <t>3.38%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.22%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:03</t>
+          <t>2026-10-08 23:44:57</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,12 +1180,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-2.18%2240</t>
+          <t>0%2240</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-2.18%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -1193,12 +1193,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.25%1,150,020</t>
+          <t>3.30%1,150,020</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.25%</t>
+          <t>3.30%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:03</t>
+          <t>2026-10-08 23:44:57</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,25 +1241,25 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+7.53%3140</t>
+          <t>-5.73%2960</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+7.53%</t>
+          <t>-5.73%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>3140</v>
+        <v>2960</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.17%800,000</t>
+          <t>3.04%800,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.17%</t>
+          <t>3.04%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.22%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:03</t>
+          <t>2026-10-08 23:44:57</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,25 +1302,25 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+5.4%839</t>
+          <t>+4.53%877</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+5.4%</t>
+          <t>+4.53%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>839</v>
+        <v>877</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.75%2,600,000</t>
+          <t>2.92%2,600,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.75%</t>
+          <t>2.92%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:03</t>
+          <t>2026-10-08 23:44:57</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,25 +1363,25 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-3.88%6805</t>
+          <t>+5.29%7165</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-3.88%</t>
+          <t>+5.29%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>6805</v>
+        <v>7165</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.49%290,000</t>
+          <t>2.66%290,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.49%</t>
+          <t>2.66%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:04</t>
+          <t>2026-10-08 23:44:59</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,25 +1424,25 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-6.51%17750</t>
+          <t>-1.49%17485</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-6.51%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>17750</v>
+        <v>17485</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.47%110,500</t>
+          <t>2.48%110,500</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.47%</t>
+          <t>2.48%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:04</t>
+          <t>2026-10-08 23:44:59</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,25 +1485,25 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-2.93%1990</t>
+          <t>-1.26%1965</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-2.93%</t>
+          <t>-1.26%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1990</v>
+        <v>1965</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.63%650,000</t>
+          <t>1.64%650,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.64%</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:04</t>
+          <t>2026-10-08 23:44:59</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,25 +1546,25 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-1.61%732</t>
+          <t>+1.64%744</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-1.61%</t>
+          <t>+1.64%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>732</v>
+        <v>744</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.57%1,700,000</t>
+          <t>1.62%1,700,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>1.62%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:04</t>
+          <t>2026-10-08 23:44:59</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,25 +1607,25 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+5.42%107</t>
+          <t>+3.27%110.5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+5.42%</t>
+          <t>+3.27%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>107</v>
+        <v>110.5</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.15%8,500,000</t>
+          <t>1.20%8,500,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.20%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:04</t>
+          <t>2026-10-08 23:44:59</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1668,16 +1668,16 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-0.15%6845</t>
+          <t>-2.7%6660</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>6845</v>
+        <v>6660</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:04</t>
+          <t>2026-10-08 23:44:59</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1729,16 +1729,16 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-0.34%5885</t>
+          <t>+0.68%5925</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-0.34%</t>
+          <t>+0.68%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>5885</v>
+        <v>5925</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:04</t>
+          <t>2026-10-08 23:44:59</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,16 +1790,16 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-2.47%5530</t>
+          <t>+0.81%5575</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-2.47%</t>
+          <t>+0.81%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>5530</v>
+        <v>5575</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:04</t>
+          <t>2026-10-08 23:44:59</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,16 +1851,16 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+0.45%335</t>
+          <t>-2.84%325.5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+0.45%</t>
+          <t>-2.84%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>335</v>
+        <v>325.5</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:04</t>
+          <t>2026-10-08 23:44:59</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,21 +1907,21 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2360致茂</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+2.13%2400</t>
+          <t>+1.94%2360</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+2.13%</t>
+          <t>+1.94%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>2400</v>
+        <v>2360</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:04</t>
+          <t>2026-10-08 23:44:59</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,21 +1968,21 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>2360致茂</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-0.43%2315</t>
+          <t>-2.92%2330</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>-2.92%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>2315</v>
+        <v>2330</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:04</t>
+          <t>2026-10-08 23:44:59</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2034,16 +2034,16 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-1.56%252</t>
+          <t>-1.19%249</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-1.56%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:04</t>
+          <t>2026-10-08 23:44:59</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,25 +2090,25 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2603長榮</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-1.69%232.5</t>
+          <t>+2.73%2070</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-1.69%</t>
+          <t>+2.73%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>232.5</v>
+        <v>2070</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>&lt;0.01%9,000</t>
+          <t>&lt;0.01%1,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2117,11 +2117,11 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>9000</v>
+        <v>1000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:04</t>
+          <t>2026-10-08 23:44:59</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,25 +2151,25 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>2603長榮</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-1.71%2015</t>
+          <t>0%232.5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-1.71%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>2015</v>
+        <v>232.5</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>&lt;0.01%1,000</t>
+          <t>&lt;0.01%9,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2178,11 +2178,11 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:04</t>
+          <t>2026-10-08 23:44:59</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,12 +2217,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-1.44%2060</t>
+          <t>0%2060</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-1.44%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:04</t>
+          <t>2026-10-08 23:44:59</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,25 +2273,25 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>3231緯創</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-2.37%185</t>
+          <t>+1.16%1740</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-2.37%</t>
+          <t>+1.16%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>185</v>
+        <v>1740</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>&lt;0.01%9,000</t>
+          <t>&lt;0.01%1,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2300,11 +2300,11 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>9000</v>
+        <v>1000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:05</t>
+          <t>2026-10-08 23:45:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,25 +2334,25 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>5347世界</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-1.99%1720</t>
+          <t>-1.84%186.5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-1.99%</t>
+          <t>-1.84%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>1720</v>
+        <v>186.5</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>&lt;0.01%1,000</t>
+          <t>&lt;0.01%9,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2361,7 +2361,7 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:05</t>
+          <t>2026-10-08 23:45:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,21 +2395,21 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>5347世界</t>
+          <t>3231緯創</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-0.52%190</t>
+          <t>+1.89%188.5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-0.52%</t>
+          <t>+1.89%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>190</v>
+        <v>188.5</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:05</t>
+          <t>2026-10-08 23:45:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2461,16 +2461,16 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+0.65%155.5</t>
+          <t>-1.61%153</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+0.65%</t>
+          <t>-1.61%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>155.5</v>
+        <v>153</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:05</t>
+          <t>2026-10-08 23:45:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,16 +2522,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+0.68%148.5</t>
+          <t>-0.67%147.5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+0.68%</t>
+          <t>-0.67%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>148.5</v>
+        <v>147.5</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:05</t>
+          <t>2026-10-08 23:45:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,16 +2583,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-1.1%989</t>
+          <t>+0.71%996</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>+0.71%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>989</v>
+        <v>996</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:05</t>
+          <t>2026-10-08 23:45:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,16 +2644,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+0.89%113</t>
+          <t>-2.65%110</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+0.89%</t>
+          <t>-2.65%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:05</t>
+          <t>2026-10-08 23:45:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,16 +2705,16 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-1.85%741</t>
+          <t>+1.08%749</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-1.85%</t>
+          <t>+1.08%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>741</v>
+        <v>749</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:05</t>
+          <t>2026-10-08 23:45:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,16 +2766,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+1.01%70</t>
+          <t>-2.43%68.3</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+1.01%</t>
+          <t>-2.43%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>70</v>
+        <v>68.3</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:05</t>
+          <t>2026-10-08 23:45:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+0.52%582</t>
+          <t>0%582</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H40" t="n">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:05</t>
+          <t>2026-10-08 23:45:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,16 +2888,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+0.44%68.7</t>
+          <t>-2.04%67.3</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+0.44%</t>
+          <t>-2.04%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>68.7</v>
+        <v>67.3</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:05</t>
+          <t>2026-10-08 23:45:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,16 +2949,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0%44.65</t>
+          <t>-1.34%44.05</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-1.34%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>44.65</v>
+        <v>44.05</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:05</t>
+          <t>2026-10-08 23:45:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,16 +3010,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+1.01%49.8</t>
+          <t>-1%49.3</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+1.01%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>49.8</v>
+        <v>49.3</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:05</t>
+          <t>2026-10-08 23:45:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,16 +3071,16 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+0.5%299.5</t>
+          <t>+1.67%304.5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+0.5%</t>
+          <t>+1.67%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>299.5</v>
+        <v>304.5</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:05</t>
+          <t>2026-10-08 23:45:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,16 +3132,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+0.66%45.75</t>
+          <t>-1.64%45</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+0.66%</t>
+          <t>-1.64%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>45.75</v>
+        <v>45</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:05</t>
+          <t>2026-10-08 23:45:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,16 +3193,16 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>+3.19%46.9</t>
+          <t>-2.35%45.8</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>+3.19%</t>
+          <t>-2.35%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>46.9</v>
+        <v>45.8</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:07</t>
+          <t>2026-10-08 23:45:01</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3254,16 +3254,16 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>+2.26%38.5</t>
+          <t>-2.47%37.55</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>-2.47%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>38.5</v>
+        <v>37.55</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:07</t>
+          <t>2026-10-08 23:45:01</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,16 +3315,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>+1.69%42.15</t>
+          <t>-2.73%41</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+1.69%</t>
+          <t>-2.73%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>42.15</v>
+        <v>41</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:07</t>
+          <t>2026-10-08 23:45:01</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,16 +3376,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-2.38%246</t>
+          <t>+0.81%248</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-2.38%</t>
+          <t>+0.81%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:07</t>
+          <t>2026-10-08 23:45:01</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>+0.23%215.5</t>
+          <t>0%215.5</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>+0.23%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H50" t="n">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:07</t>
+          <t>2026-10-08 23:45:01</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,16 +3498,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>0%145.5</t>
+          <t>+0.69%146.5</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>145.5</v>
+        <v>146.5</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>

--- a/etf_holdings/2026-10-08_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-08_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-08 23:44:57</t>
+          <t>2026-10-08 23:51:38</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-08 23:44:57</t>
+          <t>2026-10-08 23:51:38</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-08 23:44:57</t>
+          <t>2026-10-08 23:51:38</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-08 23:44:57</t>
+          <t>2026-10-08 23:51:38</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-08 23:44:57</t>
+          <t>2026-10-08 23:51:38</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-08 23:44:57</t>
+          <t>2026-10-08 23:51:38</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-08 23:44:57</t>
+          <t>2026-10-08 23:51:38</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-08 23:44:57</t>
+          <t>2026-10-08 23:51:38</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-08 23:44:57</t>
+          <t>2026-10-08 23:51:38</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-08 23:44:57</t>
+          <t>2026-10-08 23:51:38</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-08 23:44:57</t>
+          <t>2026-10-08 23:51:38</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-08 23:44:57</t>
+          <t>2026-10-08 23:51:38</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-08 23:44:57</t>
+          <t>2026-10-08 23:51:38</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-08 23:44:57</t>
+          <t>2026-10-08 23:51:38</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-08 23:44:57</t>
+          <t>2026-10-08 23:51:38</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-08 23:44:59</t>
+          <t>2026-10-08 23:51:39</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-08 23:44:59</t>
+          <t>2026-10-08 23:51:39</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-08 23:44:59</t>
+          <t>2026-10-08 23:51:39</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-08 23:44:59</t>
+          <t>2026-10-08 23:51:39</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-08 23:44:59</t>
+          <t>2026-10-08 23:51:39</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-08 23:44:59</t>
+          <t>2026-10-08 23:51:39</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-08 23:44:59</t>
+          <t>2026-10-08 23:51:39</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-08 23:44:59</t>
+          <t>2026-10-08 23:51:39</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-08 23:44:59</t>
+          <t>2026-10-08 23:51:39</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-08 23:44:59</t>
+          <t>2026-10-08 23:51:39</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-08 23:44:59</t>
+          <t>2026-10-08 23:51:39</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-08 23:44:59</t>
+          <t>2026-10-08 23:51:39</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-08 23:44:59</t>
+          <t>2026-10-08 23:51:39</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-08 23:44:59</t>
+          <t>2026-10-08 23:51:39</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-08 23:44:59</t>
+          <t>2026-10-08 23:51:39</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:00</t>
+          <t>2026-10-08 23:51:40</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:00</t>
+          <t>2026-10-08 23:51:40</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:00</t>
+          <t>2026-10-08 23:51:40</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:00</t>
+          <t>2026-10-08 23:51:40</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:00</t>
+          <t>2026-10-08 23:51:40</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:00</t>
+          <t>2026-10-08 23:51:40</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:00</t>
+          <t>2026-10-08 23:51:40</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:00</t>
+          <t>2026-10-08 23:51:40</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:00</t>
+          <t>2026-10-08 23:51:40</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:00</t>
+          <t>2026-10-08 23:51:40</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:00</t>
+          <t>2026-10-08 23:51:40</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:00</t>
+          <t>2026-10-08 23:51:40</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:00</t>
+          <t>2026-10-08 23:51:40</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:00</t>
+          <t>2026-10-08 23:51:40</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:00</t>
+          <t>2026-10-08 23:51:40</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:01</t>
+          <t>2026-10-08 23:51:41</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:01</t>
+          <t>2026-10-08 23:51:41</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:01</t>
+          <t>2026-10-08 23:51:41</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:01</t>
+          <t>2026-10-08 23:51:41</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:01</t>
+          <t>2026-10-08 23:51:41</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
